--- a/fixtures/xlsx/cell-types-mixed/input.xlsx
+++ b/fixtures/xlsx/cell-types-mixed/input.xlsx
@@ -10,25 +10,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Type</t>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>hello</t>
   </si>
   <si>
     <t>String</t>
   </si>
   <si>
-    <t>Formula</t>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Boolean</t>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
     <t>Number</t>
-  </si>
-  <si>
-    <t>Boolean</t>
-  </si>
-  <si>
-    <t>hello</t>
   </si>
 </sst>
 </file>
@@ -38,23 +38,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B3">
         <v>42</v>
@@ -62,7 +62,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -70,7 +70,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <f>B3*2</f>

--- a/fixtures/xlsx/cell-types-mixed/input.xlsx
+++ b/fixtures/xlsx/cell-types-mixed/input.xlsx
@@ -10,25 +10,25 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
-    <t>Formula</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
     <t>String</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Boolean</t>
+    <t>Number</t>
   </si>
   <si>
     <t>Value</t>
   </si>
   <si>
-    <t>Number</t>
+    <t>hello</t>
+  </si>
+  <si>
+    <t>Boolean</t>
+  </si>
+  <si>
+    <t>Formula</t>
   </si>
 </sst>
 </file>
@@ -38,23 +38,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3">
         <v>42</v>
@@ -62,7 +62,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B4" t="b">
         <v>1</v>
@@ -70,7 +70,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B5">
         <f>B3*2</f>
